--- a/artfynd/A 36244-2024 artfynd.xlsx
+++ b/artfynd/A 36244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61780648</v>
+        <v>61780773</v>
       </c>
       <c r="B2" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2666</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653517.0012530347</v>
+        <v>653523</v>
       </c>
       <c r="R2" t="n">
-        <v>6571421.259638871</v>
+        <v>6571387</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,24 +745,14 @@
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
+          <t>Rikligt med fruktkroppar på rötskadad asplåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,53 +780,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61780721</v>
+        <v>61780788</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653505.8768349481</v>
+        <v>653523</v>
       </c>
       <c r="R3" t="n">
-        <v>6571430.025380979</v>
+        <v>6571387</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,24 +850,14 @@
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På block.</t>
+          <t>På rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,52 +885,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61780773</v>
+        <v>96487227</v>
       </c>
       <c r="B4" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653522.9936238673</v>
+        <v>653493</v>
       </c>
       <c r="R4" t="n">
-        <v>6571387.200125623</v>
+        <v>6571464</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,27 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-10-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på rötskadad asplåga.</t>
+          <t>På granlåga. Gammal grov grandominerad skog med rikligt inslag av lågor och torrträd av gran. Tyvärr kraftiga angrepp av granbarkborrar som dödat många av de gamla granarna. Även gröna nyangripna granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61780779</v>
+        <v>61780614</v>
       </c>
       <c r="B5" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653522.9936238673</v>
+        <v>653523</v>
       </c>
       <c r="R5" t="n">
-        <v>6571387.200125623</v>
+        <v>6571416</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,19 +1062,9 @@
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1155,52 +1096,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61780788</v>
+        <v>61780648</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653522.9523069924</v>
+        <v>653517</v>
       </c>
       <c r="R6" t="n">
-        <v>6571388.222391658</v>
+        <v>6571421</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,24 +1167,14 @@
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rötskadad granlåga.</t>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1183,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,12 +1204,7 @@
         <v>61780662</v>
       </c>
       <c r="B7" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,12 +1221,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>653505.9550809267</v>
+        <v>653506</v>
       </c>
       <c r="R7" t="n">
-        <v>6571440.779731964</v>
+        <v>6571441</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,19 +1272,9 @@
           <t>2016-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96487251</v>
+        <v>61780737</v>
       </c>
       <c r="B8" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,38 +1317,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>653505.8355225138</v>
+        <v>653531</v>
       </c>
       <c r="R8" t="n">
-        <v>6571431.047635463</v>
+        <v>6571404</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1469,27 +1374,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På block omgärdad av kranshakmossa.</t>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1393,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1517,15 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96487355</v>
+        <v>61780796</v>
       </c>
       <c r="B9" t="n">
-        <v>93146</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,29 +1431,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neckera crispa</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängstugan, SV om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>653518.9460784947</v>
+        <v>653536</v>
       </c>
       <c r="R9" t="n">
-        <v>6571423.89805741</v>
+        <v>6571389</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,27 +1479,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Återfynd på lodyta i bergskreva. Tyvärr är många gamla beskuggande och skyddande granar angripna och dödade av granbarkborrar vilket kan komma att påverka mossan i form av uttorkning.</t>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,7 +1498,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1636,6 +1513,854 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>61780812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96439</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>653543</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6571366</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96487355</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96439</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>653519</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6571424</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd på lodyta i bergskreva. Tyvärr är många gamla beskuggande och skyddande granar angripna och dödade av granbarkborrar vilket kan komma att påverka mossan i form av uttorkning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96487406</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>653534</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6571383</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Återfynd på lodyta i skyddad skreva. Tyvärr är många gamla beskuggande och skyddande granar angripna och dödade av granbarkborrar vilket kan komma att påverka mossan i form av uttorkning.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>61780688</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>653493</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6571458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>61780779</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>653523</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6571387</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera ställen av öst- och nordostvänd trädbeskuggad bergbrant. Nyckelbiotop med många intressanta arter.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>61780721</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>653506</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6571430</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På block.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96487251</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ängstugan, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>653506</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6571431</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På block omgärdad av kranshakmossa.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>56512341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>S Daltorp, Bornsjöns NR, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>653528</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6571359</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2015-12-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2015-12-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Brant</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gammeltall</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36244-2024 artfynd.xlsx
+++ b/artfynd/A 36244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96487227</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780648</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780662</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780737</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780796</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96487355</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96487406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780688</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780779</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780721</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96487251</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2256,6 +2331,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56512341</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,8 +2441,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61780812</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>